--- a/Proiect/Proiect/Output/Rapoarte/Rezultate_Regresie_Multipla.xlsx
+++ b/Proiect/Proiect/Output/Rapoarte/Rezultate_Regresie_Multipla.xlsx
@@ -7,8 +7,7 @@
     <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
   </bookViews>
   <sheets>
-    <sheet name="Coeficienti" sheetId="1" r:id="rId1"/>
-    <sheet name="Sumar" sheetId="2" r:id="rId2"/>
+    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -352,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E8"/>
+  <dimension ref="A1:E7"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -389,16 +388,16 @@
         </is>
       </c>
       <c r="B2">
-        <v>-7.841180247833156</v>
+        <v>-6.460536023165295</v>
       </c>
       <c r="C2">
-        <v>4.465314848293607</v>
+        <v>7.837770981720324</v>
       </c>
       <c r="D2">
-        <v>-1.756019567316651</v>
+        <v>-0.8242823167751275</v>
       </c>
       <c r="E2">
-        <v>0.09519286303291623</v>
+        <v>0.4170017568518414</v>
       </c>
     </row>
     <row r="3">
@@ -408,16 +407,16 @@
         </is>
       </c>
       <c r="B3">
-        <v>1.136321860687468</v>
+        <v>0.9417441682232659</v>
       </c>
       <c r="C3">
-        <v>0.3284388905976833</v>
+        <v>0.6881086115469248</v>
       </c>
       <c r="D3">
-        <v>3.459766468640857</v>
+        <v>1.368598143403768</v>
       </c>
       <c r="E3">
-        <v>0.002624197457254128</v>
+        <v>0.1824055293058732</v>
       </c>
     </row>
     <row r="4">
@@ -427,16 +426,16 @@
         </is>
       </c>
       <c r="B4">
-        <v>0.8460921351171408</v>
+        <v>0.6214918732161552</v>
       </c>
       <c r="C4">
-        <v>0.3913129610646741</v>
+        <v>0.3054496429282696</v>
       </c>
       <c r="D4">
-        <v>2.16218786317508</v>
+        <v>2.03467866997017</v>
       </c>
       <c r="E4">
-        <v>0.043569132343804</v>
+        <v>0.05181162729382188</v>
       </c>
     </row>
     <row r="5">
@@ -446,183 +445,54 @@
         </is>
       </c>
       <c r="B5">
-        <v>0.05156026588998429</v>
+        <v>0.4561027135351299</v>
       </c>
       <c r="C5">
-        <v>0.2545276976335148</v>
+        <v>0.2360772727347883</v>
       </c>
       <c r="D5">
-        <v>0.2025723187274653</v>
+        <v>1.932006026041823</v>
       </c>
       <c r="E5">
-        <v>0.8416227467347035</v>
+        <v>0.06391529906908192</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>ln_Politie</t>
+          <t>ln_Densitate</t>
         </is>
       </c>
       <c r="B6">
-        <v>0.1897005337548554</v>
+        <v>-0.2497129330816977</v>
       </c>
       <c r="C6">
-        <v>0.4299243620182582</v>
+        <v>0.3604661735018617</v>
       </c>
       <c r="D6">
-        <v>0.4412416474012216</v>
+        <v>-0.6927499761095003</v>
       </c>
       <c r="E6">
-        <v>0.6640182969869064</v>
+        <v>0.4943823873481653</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>ln_Densitate</t>
+          <t>Est_Vest</t>
         </is>
       </c>
       <c r="B7">
-        <v>0.001871308159355385</v>
+        <v>0.05255646585264516</v>
       </c>
       <c r="C7">
-        <v>0.1878694647477448</v>
+        <v>1.002751297708216</v>
       </c>
       <c r="D7">
-        <v>0.009960682870247269</v>
+        <v>0.0524122641105155</v>
       </c>
       <c r="E7">
-        <v>0.9921565010313369</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>Membru_UE</t>
-        </is>
-      </c>
-      <c r="B8">
-        <v>0.08828501322068324</v>
-      </c>
-      <c r="C8">
-        <v>0.7210191972372517</v>
-      </c>
-      <c r="D8">
-        <v>0.1224447470455256</v>
-      </c>
-      <c r="E8">
-        <v>0.903832662158446</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L2"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1" s="1" customFormat="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>r.squared</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>adj.r.squared</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>sigma</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>statistic</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>p.value</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>df</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>logLik</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>AIC</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>BIC</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>deviance</t>
-        </is>
-      </c>
-      <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>df.residual</t>
-        </is>
-      </c>
-      <c r="L1" s="1" t="inlineStr">
-        <is>
-          <t>nobs</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2">
-        <v>0.8229080841791986</v>
-      </c>
-      <c r="B2">
-        <v>0.7669843212884192</v>
-      </c>
-      <c r="C2">
-        <v>0.7897809765711914</v>
-      </c>
-      <c r="D2">
-        <v>14.71481963376391</v>
-      </c>
-      <c r="E2">
-        <v>3.070539263654778E-06</v>
-      </c>
-      <c r="F2">
-        <v>6</v>
-      </c>
-      <c r="G2">
-        <v>-26.67886356122082</v>
-      </c>
-      <c r="H2">
-        <v>69.35772712244163</v>
-      </c>
-      <c r="I2">
-        <v>79.42249942661348</v>
-      </c>
-      <c r="J2">
-        <v>11.85132582812115</v>
-      </c>
-      <c r="K2">
-        <v>19</v>
-      </c>
-      <c r="L2">
-        <v>26</v>
+        <v>0.9585860649321369</v>
       </c>
     </row>
   </sheetData>
